--- a/docs/Decodifiche/100_dec_versione.xlsx
+++ b/docs/Decodifiche/100_dec_versione.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="124">
   <si>
     <t>ID</t>
   </si>
@@ -372,6 +372,18 @@
   </si>
   <si>
     <t>2025-12-21 00:00:00.0</t>
+  </si>
+  <si>
+    <t>2026-10-24 16:23:18.0</t>
+  </si>
+  <si>
+    <t>100030</t>
+  </si>
+  <si>
+    <t>1.49.x</t>
+  </si>
+  <si>
+    <t>2026-02-24 00:00:00.0</t>
   </si>
 </sst>
 </file>
@@ -430,7 +442,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="7.7265625" customWidth="true" bestFit="true"/>
@@ -961,10 +973,27 @@
         <v>119</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>118</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>121</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Decodifiche/100_dec_versione.xlsx
+++ b/docs/Decodifiche/100_dec_versione.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="128">
   <si>
     <t>ID</t>
   </si>
@@ -384,6 +384,18 @@
   </si>
   <si>
     <t>2026-02-24 00:00:00.0</t>
+  </si>
+  <si>
+    <t>2026-11-26 18:08:54.0</t>
+  </si>
+  <si>
+    <t>100031</t>
+  </si>
+  <si>
+    <t>1.50.x</t>
+  </si>
+  <si>
+    <t>2026-03-26 00:00:00.0</t>
   </si>
 </sst>
 </file>
@@ -442,7 +454,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="7.7265625" customWidth="true" bestFit="true"/>
@@ -990,10 +1002,27 @@
         <v>123</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>121</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>125</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Decodifiche/100_dec_versione.xlsx
+++ b/docs/Decodifiche/100_dec_versione.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="132">
   <si>
     <t>ID</t>
   </si>
@@ -396,6 +396,18 @@
   </si>
   <si>
     <t>2026-03-26 00:00:00.0</t>
+  </si>
+  <si>
+    <t>2026-12-27 17:24:05.0</t>
+  </si>
+  <si>
+    <t>100032</t>
+  </si>
+  <si>
+    <t>1.51.x</t>
+  </si>
+  <si>
+    <t>2026-04-27 00:00:00.0</t>
   </si>
 </sst>
 </file>
@@ -454,7 +466,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="7.7265625" customWidth="true" bestFit="true"/>
@@ -1019,10 +1031,27 @@
         <v>127</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>125</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>129</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Decodifiche/100_dec_versione.xlsx
+++ b/docs/Decodifiche/100_dec_versione.xlsx
@@ -101,7 +101,7 @@
     <t>2023-11-13 00:00:00.0</t>
   </si>
   <si>
-    <t>2024-03-20 00:00:00.0</t>
+    <t>2024-03-19 16:48:09.0</t>
   </si>
   <si>
     <t>100007</t>
@@ -110,10 +110,10 @@
     <t>1.22.x</t>
   </si>
   <si>
-    <t>2023-12-21 00:00:00.0</t>
-  </si>
-  <si>
-    <t>2024-04-16 00:00:00.0</t>
+    <t>2023-12-20 16:48:09.0</t>
+  </si>
+  <si>
+    <t>2024-04-18 09:51:11.0</t>
   </si>
   <si>
     <t>100008</t>
@@ -122,10 +122,10 @@
     <t>1.23.x</t>
   </si>
   <si>
-    <t>2024-01-17 00:00:00.0</t>
-  </si>
-  <si>
-    <t>2024-05-19 00:00:00.0</t>
+    <t>2024-01-19 09:51:02.0</t>
+  </si>
+  <si>
+    <t>2024-05-22 09:59:34.0</t>
   </si>
   <si>
     <t>100009</t>
@@ -134,10 +134,10 @@
     <t>1.24.x</t>
   </si>
   <si>
-    <t>2024-02-19 00:00:00.0</t>
-  </si>
-  <si>
-    <t>2024-06-11 00:00:00.0</t>
+    <t>2024-02-21 09:59:31.0</t>
+  </si>
+  <si>
+    <t>2024-06-09 11:36:59.0</t>
   </si>
   <si>
     <t>100010</t>
@@ -149,7 +149,7 @@
     <t>2024-03-11 00:00:00.0</t>
   </si>
   <si>
-    <t>2024-06-23 00:00:00.0</t>
+    <t>2024-06-25 00:00:00.0</t>
   </si>
   <si>
     <t>100011</t>
@@ -161,7 +161,7 @@
     <t>2024-03-27 00:00:00.0</t>
   </si>
   <si>
-    <t>2024-10-01 00:00:00.0</t>
+    <t>2024-07-29 00:00:00.0</t>
   </si>
   <si>
     <t>100012</t>
@@ -182,7 +182,7 @@
     <t>1.29.x</t>
   </si>
   <si>
-    <t>2024-05-29 00:00:00.0</t>
+    <t>2024-05-30 00:00:00.0</t>
   </si>
   <si>
     <t>2024-12-01 00:00:00.0</t>
@@ -194,10 +194,10 @@
     <t>1.30.x</t>
   </si>
   <si>
-    <t>2024-06-25 00:00:00.0</t>
-  </si>
-  <si>
-    <t>2025-01-25 00:00:00.0</t>
+    <t>2024-06-27 00:00:00.0</t>
+  </si>
+  <si>
+    <t>2025-01-31 00:00:00.0</t>
   </si>
   <si>
     <t>100015</t>
@@ -206,10 +206,10 @@
     <t>1.32.x</t>
   </si>
   <si>
-    <t>2024-07-25 00:00:00.0</t>
-  </si>
-  <si>
-    <t>2025-05-24 00:00:00.0</t>
+    <t>2024-07-31 00:00:00.0</t>
+  </si>
+  <si>
+    <t>2025-03-31 00:00:00.0</t>
   </si>
   <si>
     <t>100016</t>
@@ -218,7 +218,7 @@
     <t>1.33.x</t>
   </si>
   <si>
-    <t>2024-09-24 00:00:00.0</t>
+    <t>2024-10-03 00:00:00.0</t>
   </si>
   <si>
     <t>2025-09-30 00:00:00.0</t>
@@ -230,106 +230,106 @@
     <t>1.34.x</t>
   </si>
   <si>
-    <t>2024-10-29 00:00:00.0</t>
+    <t>2024-11-04 00:00:00.0</t>
+  </si>
+  <si>
+    <t>2025-07-04 00:00:00.0</t>
+  </si>
+  <si>
+    <t>100018</t>
+  </si>
+  <si>
+    <t>1.35.x</t>
+  </si>
+  <si>
+    <t>2024-11-29 00:00:00.0</t>
+  </si>
+  <si>
+    <t>2025-07-29 00:00:00.0</t>
+  </si>
+  <si>
+    <t>100019</t>
+  </si>
+  <si>
+    <t>1.36.x</t>
+  </si>
+  <si>
+    <t>2024-12-19 00:00:00.0</t>
+  </si>
+  <si>
+    <t>2025-08-19 00:00:00.0</t>
+  </si>
+  <si>
+    <t>100020</t>
+  </si>
+  <si>
+    <t>1.37.x</t>
+  </si>
+  <si>
+    <t>2025-02-04 00:00:00.0</t>
+  </si>
+  <si>
+    <t>2026-01-01 00:00:00.0</t>
+  </si>
+  <si>
+    <t>100021</t>
+  </si>
+  <si>
+    <t>1.38.x</t>
+  </si>
+  <si>
+    <t>2025-02-26 00:00:00.0</t>
+  </si>
+  <si>
+    <t>2025-12-01 08:48:09.0</t>
+  </si>
+  <si>
+    <t>100022</t>
+  </si>
+  <si>
+    <t>1.39.x</t>
+  </si>
+  <si>
+    <t>2025-04-01 00:00:00.0</t>
+  </si>
+  <si>
+    <t>2026-01-29 17:03:54.0</t>
+  </si>
+  <si>
+    <t>100023</t>
+  </si>
+  <si>
+    <t>1.41.x</t>
+  </si>
+  <si>
+    <t>2025-05-29 00:00:00.0</t>
+  </si>
+  <si>
+    <t>2026-02-28 23:45:35.0</t>
+  </si>
+  <si>
+    <t>100024</t>
+  </si>
+  <si>
+    <t>1.42.x</t>
+  </si>
+  <si>
+    <t>2025-06-29 00:00:00.0</t>
+  </si>
+  <si>
+    <t>2026-03-30 13:30:40.0</t>
+  </si>
+  <si>
+    <t>100025</t>
+  </si>
+  <si>
+    <t>1.43.x</t>
   </si>
   <si>
     <t>2025-07-30 00:00:00.0</t>
   </si>
   <si>
-    <t>100018</t>
-  </si>
-  <si>
-    <t>1.35.x</t>
-  </si>
-  <si>
-    <t>2024-12-02 00:00:00.0</t>
-  </si>
-  <si>
-    <t>2025-08-18 00:00:00.0</t>
-  </si>
-  <si>
-    <t>100019</t>
-  </si>
-  <si>
-    <t>1.36.x</t>
-  </si>
-  <si>
-    <t>2024-12-18 00:00:00.0</t>
-  </si>
-  <si>
-    <t>2025-09-28 00:00:00.0</t>
-  </si>
-  <si>
-    <t>100020</t>
-  </si>
-  <si>
-    <t>1.37.x</t>
-  </si>
-  <si>
-    <t>2025-01-28 00:00:00.0</t>
-  </si>
-  <si>
-    <t>2026-01-01 00:00:00.0</t>
-  </si>
-  <si>
-    <t>100021</t>
-  </si>
-  <si>
-    <t>1.38.x</t>
-  </si>
-  <si>
-    <t>2025-02-25 00:00:00.0</t>
-  </si>
-  <si>
-    <t>2025-11-27 00:00:00.0</t>
-  </si>
-  <si>
-    <t>100022</t>
-  </si>
-  <si>
-    <t>1.39.x</t>
-  </si>
-  <si>
-    <t>2025-03-27 00:00:00.0</t>
-  </si>
-  <si>
-    <t>2026-01-26 18:59:04.0</t>
-  </si>
-  <si>
-    <t>100023</t>
-  </si>
-  <si>
-    <t>1.41.x</t>
-  </si>
-  <si>
-    <t>2025-05-26 00:00:00.0</t>
-  </si>
-  <si>
-    <t>2026-02-25 12:07:32.0</t>
-  </si>
-  <si>
-    <t>100024</t>
-  </si>
-  <si>
-    <t>1.42.x</t>
-  </si>
-  <si>
-    <t>2025-06-25 00:00:00.0</t>
-  </si>
-  <si>
-    <t>2026-03-29 16:52:46.0</t>
-  </si>
-  <si>
-    <t>100025</t>
-  </si>
-  <si>
-    <t>1.43.x</t>
-  </si>
-  <si>
-    <t>2025-07-29 00:00:00.0</t>
-  </si>
-  <si>
-    <t>2026-05-26 17:22:25.0</t>
+    <t>2026-05-29 13:00:36.0</t>
   </si>
   <si>
     <t>100026</t>
@@ -338,10 +338,10 @@
     <t>1.44.x</t>
   </si>
   <si>
-    <t>2025-09-26 00:00:00.0</t>
-  </si>
-  <si>
-    <t>2026-06-28 18:04:39.0</t>
+    <t>2025-09-29 00:00:00.0</t>
+  </si>
+  <si>
+    <t>2026-06-30 09:53:35.0</t>
   </si>
   <si>
     <t>100027</t>
@@ -350,10 +350,10 @@
     <t>1.46.x</t>
   </si>
   <si>
-    <t>2025-10-28 00:00:00.0</t>
-  </si>
-  <si>
-    <t>2026-08-21 21:34:20.0</t>
+    <t>2025-10-30 00:00:00.0</t>
+  </si>
+  <si>
+    <t>2026-08-22 14:23:16.0</t>
   </si>
   <si>
     <t>100028</t>
@@ -362,52 +362,52 @@
     <t>1.48.x</t>
   </si>
   <si>
-    <t>2025-12-15 00:00:00.0</t>
+    <t>2025-12-22 00:00:00.0</t>
+  </si>
+  <si>
+    <t>2026-08-22 15:14:40.0</t>
+  </si>
+  <si>
+    <t>100029</t>
+  </si>
+  <si>
+    <t>2026-11-02 08:14:30.0</t>
+  </si>
+  <si>
+    <t>100030</t>
+  </si>
+  <si>
+    <t>1.49.x</t>
+  </si>
+  <si>
+    <t>2026-03-02 00:00:00.0</t>
+  </si>
+  <si>
+    <t>2026-11-30 09:28:04.0</t>
+  </si>
+  <si>
+    <t>100031</t>
+  </si>
+  <si>
+    <t>1.50.x</t>
+  </si>
+  <si>
+    <t>2026-03-31 00:00:00.0</t>
+  </si>
+  <si>
+    <t>2027-01-04 10:27:45.0</t>
+  </si>
+  <si>
+    <t>100032</t>
+  </si>
+  <si>
+    <t>1.51.x</t>
+  </si>
+  <si>
+    <t>2026-05-04 00:00:00.0</t>
   </si>
   <si>
     <t>9999-12-31 00:00:00.0</t>
-  </si>
-  <si>
-    <t>100029</t>
-  </si>
-  <si>
-    <t>2025-12-21 00:00:00.0</t>
-  </si>
-  <si>
-    <t>2026-10-24 16:23:18.0</t>
-  </si>
-  <si>
-    <t>100030</t>
-  </si>
-  <si>
-    <t>1.49.x</t>
-  </si>
-  <si>
-    <t>2026-02-24 00:00:00.0</t>
-  </si>
-  <si>
-    <t>2026-11-26 18:08:54.0</t>
-  </si>
-  <si>
-    <t>100031</t>
-  </si>
-  <si>
-    <t>1.50.x</t>
-  </si>
-  <si>
-    <t>2026-03-26 00:00:00.0</t>
-  </si>
-  <si>
-    <t>2026-12-27 17:24:05.0</t>
-  </si>
-  <si>
-    <t>100032</t>
-  </si>
-  <si>
-    <t>1.51.x</t>
-  </si>
-  <si>
-    <t>2026-04-27 00:00:00.0</t>
   </si>
 </sst>
 </file>
@@ -994,10 +994,10 @@
         <v>115</v>
       </c>
       <c r="C31" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D31" s="2" t="s">
         <v>119</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>120</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>118</v>
@@ -1005,53 +1005,53 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="C32" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="D32" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="D32" s="2" t="s">
-        <v>124</v>
-      </c>
       <c r="E32" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B33" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="C33" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="D33" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="D33" s="2" t="s">
-        <v>128</v>
-      </c>
       <c r="E33" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B34" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="C34" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="D34" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="D34" s="2" t="s">
-        <v>117</v>
-      </c>
       <c r="E34" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Decodifiche/100_dec_versione.xlsx
+++ b/docs/Decodifiche/100_dec_versione.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="136">
   <si>
     <t>ID</t>
   </si>
@@ -405,6 +405,18 @@
   </si>
   <si>
     <t>2026-05-04 00:00:00.0</t>
+  </si>
+  <si>
+    <t>2027-02-04 09:39:09.0</t>
+  </si>
+  <si>
+    <t>100033</t>
+  </si>
+  <si>
+    <t>1.52.x</t>
+  </si>
+  <si>
+    <t>2026-06-04 00:00:00.0</t>
   </si>
   <si>
     <t>9999-12-31 00:00:00.0</t>
@@ -466,7 +478,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="7.7265625" customWidth="true" bestFit="true"/>
@@ -1054,6 +1066,23 @@
         <v>128</v>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/docs/Decodifiche/100_dec_versione.xlsx
+++ b/docs/Decodifiche/100_dec_versione.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="140">
   <si>
     <t>ID</t>
   </si>
@@ -417,6 +417,18 @@
   </si>
   <si>
     <t>2026-06-04 00:00:00.0</t>
+  </si>
+  <si>
+    <t>2027-02-28 10:18:34.0</t>
+  </si>
+  <si>
+    <t>100034</t>
+  </si>
+  <si>
+    <t>1.53.x</t>
+  </si>
+  <si>
+    <t>2026-06-30 00:00:00.0</t>
   </si>
   <si>
     <t>9999-12-31 00:00:00.0</t>
@@ -478,7 +490,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="7.7265625" customWidth="true" bestFit="true"/>
@@ -1083,6 +1095,23 @@
         <v>132</v>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
